--- a/public/upload/export_excel/รายงานหนี้สูญ.xlsx
+++ b/public/upload/export_excel/รายงานหนี้สูญ.xlsx
@@ -15,9 +15,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="13">
-  <si>
-    <t>รายงานหนี้สูญ วันที่ 17/08/2025</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="10">
+  <si>
+    <t>รายงานหนี้สูญ วันที่ 25/08/2025</t>
   </si>
   <si>
     <t>ห้อง</t>
@@ -45,15 +45,6 @@
   </si>
   <si>
     <t>วันที่</t>
-  </si>
-  <si>
-    <t>A102</t>
-  </si>
-  <si>
-    <t>8/2025</t>
-  </si>
-  <si>
-    <t>15/08/2025</t>
   </si>
 </sst>
 </file>
@@ -396,7 +387,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -441,31 +432,6 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="1">
-        <v>5000</v>
-      </c>
-      <c r="E3" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="F3" s="1">
-        <v>455.0</v>
-      </c>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
   </sheetData>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/upload/export_excel/รายงานหนี้สูญ.xlsx
+++ b/public/upload/export_excel/รายงานหนี้สูญ.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="10">
   <si>
-    <t>รายงานหนี้สูญ วันที่ 25/08/2025</t>
+    <t>รายงานหนี้สูญ วันที่ 28/11/2025</t>
   </si>
   <si>
     <t>ห้อง</t>
